--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Database Engineer Specialist</t>
+          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Truliant Federal Credit Union</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
+          <t>https://www.indeed.com/viewjob?jk=543aa65a317360b9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
+          <t>https://www.indeed.com/viewjob?jk=330e1f6bd510ff4c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Database Engineer Specialist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Truliant Federal Credit Union</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Systems Engineer Associate (Hybrid)</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb7385f8eabf223</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Inventory and POS Revenue Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6 points</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60f755c35383fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LexisNexis</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, Azure, Scala, Data Modeling, CI/CD, Azure DevOps, Maven, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a67ac5f9356155e</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,382 +2386,382 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2e568d26a7474</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05320397bd7ad11d</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdd0456f944935c</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5420dd834c766a13</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f966fab31401d8</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbd6f491febc357</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5433979dcc94205</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb2f35550709548</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>AI Analytics Engineer, AVS Digital Transformation</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d61c2f35115432a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2792,528 +2792,528 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2ee244ec33d3bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=003d2872a367f7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bc2289938f4405</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74208cf6d199690c</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46fbb4dae64e6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc2c5dd276794f4</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce52e0c830627747</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43794edb406b30a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da866dadfc398bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f94e35b00dfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Engineer II – Big Data / Apptio / ETL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de3319f80362e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2e925594caa302</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e845a4455074218</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17a6d6d120fd53</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628959077feac569</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4148085200fe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86534d2a234ccfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e095783be6be66</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c1d57f3476a801</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0237c9617e55c87f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering Full-stack Developer- Consultant</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7997ac4818bd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>Engineer II – Java / Node.js / Python</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,40 +4031,2140 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Williamsville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Enterprise Data &amp; BI Architect II</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>University of Central Florida</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Infoorigin Inc</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>Data Architect</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Second Round, LP</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
         <is>
           <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f111d99c03d0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=eda6c680f40e7a46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior (Must be in UT, FL, or GA)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cooperative Benefits Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, ECS, RDS, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33af3f3ce9d604c3</t>
+          <t>https://www.indeed.com/viewjob?jk=52f111d99c03d0f9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Analytics Warehousing</t>
+          <t>Data Engineer - Senior (Must be in UT, FL, or GA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Cooperative Benefits Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>AWS, Glue, Lambda, Redshift, ECS, RDS, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
+          <t>https://www.indeed.com/viewjob?jk=33af3f3ce9d604c3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,87 +661,87 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
+          <t>https://www.indeed.com/viewjob?jk=895c9e3526ed7090</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Senior Engineer, Data Analytics Warehousing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=543aa65a317360b9</t>
+          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
         </is>
       </c>
     </row>
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330e1f6bd510ff4c</t>
+          <t>https://www.indeed.com/viewjob?jk=543aa65a317360b9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Database Engineer Specialist</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truliant Federal Credit Union</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=330e1f6bd510ff4c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
+          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
+          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Truliant Federal Credit Union</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,104 +1011,104 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Dataflow, Scala, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer II – Big Data / Apptio / ETL</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7e21b0243e5dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6477669f0e5f126</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
@@ -3933,17 +3933,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer II – Java / Node.js / Python</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b275c248953625e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
+          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
+          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
+          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
+          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
+          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
+          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
+          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
+          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
+          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
+          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
+          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
+          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
+          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
+          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
+          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
+          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
+          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
+          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
+          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
+          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
+          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
+          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
+          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
+          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
+          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
+          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
+          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
+          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
+          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
+          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Second Round, LP</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>
       </c>
     </row>
@@ -6132,41 +6132,6 @@
       <c r="G163" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Second Round, LP</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=543aa65a317360b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
         </is>
       </c>
     </row>
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330e1f6bd510ff4c</t>
+          <t>https://www.indeed.com/viewjob?jk=543aa65a317360b9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=330e1f6bd510ff4c</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
@@ -3758,25 +3758,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
+          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
+          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
+          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
+          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
+          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
+          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
+          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
+          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
+          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
+          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
+          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
+          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
+          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
+          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
+          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
+          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
+          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
+          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
+          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
+          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
+          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
+          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
+          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
+          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
+          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
+          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
+          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
+          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Second Round, LP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
@@ -6132,6 +6132,41 @@
       <c r="G163" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Second Round, LP</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
@@ -1063,52 +1063,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
+          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
+          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
+          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
+          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
+          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
+          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
+          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
+          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
+          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
+          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
+          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
+          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
+          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
+          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
+          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
+          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
+          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
+          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
+          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
+          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
+          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
+          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
+          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
+          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Dev Engineer (Python, AWS)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Second Round, LP</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6130,41 +6130,6 @@
         </is>
       </c>
       <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Second Round, LP</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=543aa65a317360b9</t>
         </is>
       </c>
     </row>
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=543aa65a317360b9</t>
+          <t>https://www.indeed.com/viewjob?jk=330e1f6bd510ff4c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330e1f6bd510ff4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
         </is>
       </c>
     </row>
@@ -2323,52 +2323,52 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>IT Solutions Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Scala, Kafka, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7803539b5e31ca</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
+          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
+          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
+          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
+          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
+          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
+          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
+          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
+          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
+          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
+          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
+          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
+          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
+          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
+          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
+          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
+          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
+          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
+          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
+          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
+          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
+          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
+          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
+          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
+          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
+          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Second Round, LP</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Software Dev Engineer (Python, AWS)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Second Round, LP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,7 +6131,77 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Software Dev Engineer (Python, AWS)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Brillius</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Database Engineer Specialist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>Truliant Federal Credit Union</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=543aa65a317360b9</t>
+          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Express</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, BigQuery, Scala, Oracle, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330e1f6bd510ff4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Database Engineer Specialist</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truliant Federal Credit Union</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,139 +941,139 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,102 +2596,102 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IT Solutions Architect</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Scala, Kafka, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7803539b5e31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Cloud Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Second Round, LP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Product Architect</t>
+          <t>Software Dev Engineer (Python, AWS)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4205,2001 +4205,6 @@
         </is>
       </c>
       <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Mechanicsburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Dayton, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Midland, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Fresno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>University of Central Florida</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Infoorigin Inc</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Second Round, LP</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Mission Pet Health</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Software Dev Engineer (Python, AWS)</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Brillius</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
         </is>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>ELCOR Tax &amp; Accounting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895c9e3526ed7090</t>
+          <t>https://www.indeed.com/viewjob?jk=1916e0848359ede0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Analytics Warehousing</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
+          <t>https://www.indeed.com/viewjob?jk=895c9e3526ed7090</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Senior Engineer, Data Analytics Warehousing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,139 +731,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Database Engineer Specialist</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Truliant Federal Credit Union</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
+          <t>Database Engineer Specialist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Truliant Federal Credit Union</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
+          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,69 +2236,69 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca70a174fda1627</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Second Round, LP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Software Dev Engineer (Python, AWS)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Second Round, LP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,42 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Software Dev Engineer (Python, AWS)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Brillius</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior (Must be in UT, FL, or GA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cooperative Benefits Group</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, ECS, RDS, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Athena, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33af3f3ce9d604c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3a7fa88191eb9b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer - Senior (Must be in UT, FL, or GA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ELCOR Tax &amp; Accounting</t>
+          <t>Cooperative Benefits Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, ECS, RDS, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916e0848359ede0</t>
+          <t>https://www.indeed.com/viewjob?jk=33af3f3ce9d604c3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>ELCOR Tax &amp; Accounting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895c9e3526ed7090</t>
+          <t>https://www.indeed.com/viewjob?jk=1916e0848359ede0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Analytics Warehousing</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
+          <t>https://www.indeed.com/viewjob?jk=895c9e3526ed7090</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Senior Engineer, Data Analytics Warehousing</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,139 +766,139 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Database Engineer Specialist</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truliant Federal Credit Union</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
+          <t>Database Engineer Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Truliant Federal Credit Union</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
+          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,69 +2271,69 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,59 +3681,59 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Dev Engineer (Python, AWS)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Dev Engineer (Python, AWS)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Second Round, LP</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,15 +4161,50 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Second Round, LP</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,69 +2271,69 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,59 +3681,59 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Dev Engineer (Python, AWS)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Dev Engineer (Python, AWS)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>Second Round, LP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4170,41 +4170,6 @@
         </is>
       </c>
       <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Second Round, LP</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,69 +2271,69 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Second Round, LP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Dev Engineer (Python, AWS)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Second Round, LP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,112 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Enterprise Data &amp; BI Architect II</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>University of Central Florida</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Dev Engineer (Python, AWS)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Brillius</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,52 +853,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - Enterprise Data Storage and Consumption</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c2046eb45f5f85</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,104 +976,104 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1124c41db4d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,94 +2561,94 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Second Round, LP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Software Dev Engineer (Python, AWS)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Second Round, LP</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,77 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Mission Pet Health</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Software Dev Engineer (Python, AWS)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Brillius</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Database Engineer Specialist</t>
+          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Truliant Federal Credit Union</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Truliant Federal Credit Union</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
@@ -2148,25 +2148,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,69 +2236,69 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Dev Engineer (Python, AWS)</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,42 +4171,2002 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Second Round, LP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b463ca1eaf373d</t>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Infoorigin Inc</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Enterprise Data &amp; BI Architect II</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>University of Central Florida</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Software Dev Engineer (Python, AWS)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Brillius</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,87 +643,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior (Must be in UT, FL, or GA)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cooperative Benefits Group</t>
+          <t>ELCOR Tax &amp; Accounting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, ECS, RDS, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33af3f3ce9d604c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1916e0848359ede0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ELCOR Tax &amp; Accounting</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916e0848359ede0</t>
+          <t>https://www.indeed.com/viewjob?jk=895c9e3526ed7090</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Engineer, Data Analytics Warehousing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895c9e3526ed7090</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Analytics Warehousing</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
+          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Database Engineer Specialist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Truliant Federal Credit Union</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
+          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Database Engineer Specialist</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truliant Federal Credit Union</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,94 +951,94 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,94 +2526,94 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
@@ -2897,11 +2897,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wahl Clipper Corporation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wahl Clipper Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,2222 +3951,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbf4f8d1bef0bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Williamsville, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Mechanicsburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Dayton, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Midland, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Fresno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>SQL Database Administrator-Richmond, VA-Hybrid</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Infoorigin Inc</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a6462421d5ba59</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>University of Central Florida</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Mission Pet Health</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d64ad500888319</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Software Dev Engineer (Python, AWS)</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Brillius</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71529c637e66b97e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IAM Consultant</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.4</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec47adf429b46ec</t>
+          <t>https://www.indeed.com/viewjob?jk=89a9927f99af6704</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a9927f99af6704</t>
+          <t>https://www.indeed.com/viewjob?jk=eda6c680f40e7a46</t>
         </is>
       </c>
     </row>
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda6c680f40e7a46</t>
+          <t>https://www.indeed.com/viewjob?jk=52f111d99c03d0f9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Athena, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f111d99c03d0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3a7fa88191eb9b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ochsner Health</t>
+          <t>ELCOR Tax &amp; Accounting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3a7fa88191eb9b</t>
+          <t>https://www.indeed.com/viewjob?jk=1916e0848359ede0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ELCOR Tax &amp; Accounting</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916e0848359ede0</t>
+          <t>https://www.indeed.com/viewjob?jk=895c9e3526ed7090</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,112 +696,112 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895c9e3526ed7090</t>
+          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Analytics Warehousing</t>
+          <t>Database Engineer Specialist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Truliant Federal Credit Union</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
+          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c5c77bab43780c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Database Engineer Specialist</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Truliant Federal Credit Union</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,129 +2316,129 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43b502fbfeeaf45</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151fd4e643ac3572</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Spark, Kafka, Snowflake</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53eb89fc9a689b98</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3177,11 +3177,11 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Hadoop, Scala, Snowflake, SQL Server, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5725689c49c519a</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3435,531 +3435,6 @@
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Wahl Clipper Corporation</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Sterling, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Power BI, Tableau, MLOps, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Deltek</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>AAA Central Penn</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Hydrafacial</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Lakewood, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Python + AI + AWS Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Houston, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Azure Network Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=705a4dba3e7e2af4</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Scala, Data Modeling, MLOps, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>University of Central Florida</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
@@ -2218,52 +2218,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Governance Consultant (Databricks &amp; Unity Catalog)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Hive, Spark, PySpark, Databricks Lakehouse, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a115a9d1c46f9873</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3330,111 +3330,6 @@
         </is>
       </c>
       <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>University of Central Florida</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1cded0806fe853</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Texplorers Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, Snowflake Schema, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663b281c03f3187</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,87 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>University of Central Florida</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -2498,25 +2498,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Database Engineer Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truliant Federal Credit Union</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde10a97ad4e1bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
@@ -853,52 +853,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,69 +2026,69 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,69 +2166,69 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e0fb095260347</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,77 +2761,77 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect - T7</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NielsenIQ</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2897,11 +2897,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2d9ec8a239efae</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Enterprise Data &amp; BI Architect II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>University of Central Florida</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,190 +3076,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>University of Central Florida</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>DevOps Engineer – Azure Platform</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>

--- a/results/job_matches_2026-03-14.xlsx
+++ b/results/job_matches_2026-03-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c60e45ca869fa9d5</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Senior</t>
+          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Databricks, Unity Catalog, Hive, HBase, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Apache Flink, Java, Snowflake, AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2084f99621e86</t>
+          <t>https://www.indeed.com/viewjob?jk=aad1de821a93e0b1</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, SNS, ECS, RDS, Azure, GCP</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2df53c2e15baa1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbbc7abc8558940f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92cfc17b08676f</t>
+          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1163a25538777564</t>
+          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18dc7626b24c6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90f6d7e770c684</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ea38d66cf35a45</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e76761739b845a</t>
+          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97d3f9912a6aa4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ddbe576ba878f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a19269c4c953c25</t>
+          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf513bfdddeaba0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cfadfa3605958</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ec2af98246c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8551cb62948ff6be</t>
+          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02948236d900de33</t>
+          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8434dd81ac921342</t>
+          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5090add5590d3e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17dce2bcdc50f88</t>
+          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0473be1462ae4006</t>
+          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573d741d5a0ba5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9da6245a78e25e</t>
+          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f260b5d4d7eb65de</t>
+          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48fe6be9906b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d1db145af0c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c87da65c91d95e</t>
+          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decb45488ba63779</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7fbf4379f8e69</t>
+          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,129 +1931,129 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ec8078d498578a</t>
+          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineering Foundry - Software Engineering - Full-stack Developer - Senior Consultant</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ad7a65cfc17627</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9218ff5eb1a7d2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, ECS, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14604263ad5baf02</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>WorldPac</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WorldPac</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecb5406f2fc6477</t>
+          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
+          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5013ef8bbacceb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=93dd48e233a7087c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Los Angeles Capital Management</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Los Angeles Capital Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ECS, Azure, Databricks, Snowflake, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e11f08f7bc087c2</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, MLOps</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca1d29efb08280</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2b77b3591be602</t>
+          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, ETL, dbt, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824071e80e8483d8</t>
+          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior Enterprise Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>University of the Incarnate Word</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95119289bfecd34e</t>
+          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a179fc6f0cf1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Enterprise Developer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>University of the Incarnate Word</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53620e4f5fd667ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c300b87ee62d92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2d9536747a0284</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (React, Python, Java, Go) *Hybrid*</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823ad43221d82d70</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Python + AI + AWS Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Scala, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
+          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf5e2df2b8b26e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55835033d967ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b0dd859ab8bea9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6345d3ebbb19b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b269236fe5dd590d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8651b85653d1da21</t>
+          <t>https://www.indeed.com/viewjob?jk=6928439d127dae90</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; BI Architect II</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>University of Central Florida</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d088a133aaee12a5</t>
+          <t>https://www.indeed.com/viewjob?jk=44bd5c224c794422</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Azure Platform</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,50 +3041,1835 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
+          <t>https://www.indeed.com/viewjob?jk=2402e48aae14f2bf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60f2560c1ac29b00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c738cb236c4be99e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21a41e1558d93f05</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc98e5257da54458</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481725659892a886</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edc8701fc4aedf6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc2dac136ec8d9eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b41603e4856829a</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=006dd34248913d38</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f8d8661d7e10fa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7050d3f8c32a0b3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=903e2ab514fbf239</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc3495b3f5635fcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1f316fd496edd4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec438083677e5fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc92c7d6c9603394</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7600cd59c0b42a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03348a0359b2f90d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b2f57f1f6fb55fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2056b0570fd2e935</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=375887fa5a11a9d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f3acecebf1892fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4a1d581cb791fe3</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50be0e83c8c83b2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8435933e77ed1c3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9bb12403fb36ac5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f5ba39efcf9a665</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53724b813ca926d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=478dfa3ea24b0750</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ba44c570d6de6eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19f643bc2777a11a</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=115873817df4f14f</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=508aa15643212527</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65758b7607e2d02c</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90bdb794d0651ce6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1933817158de617</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dab028089559939</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75ff12e8b301e85a</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd9a8e286ed0e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e233a7e29410184</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e27a11fd42d0d15c</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c92cacfa07098d65</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65bc380120b82d91</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc75a85b5e421396</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c127b2b5cb050a40</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=437d7df9e54a3512</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8f98d44565f0502</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccc12def6cbbfcd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d9f9a3ce7b49a24</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=449cafbb6b28d5f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DevOps Engineer – Azure Platform</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Skyworks Solutions</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Irvine, CA, US USA</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>
